--- a/Team-Data/2011-12/2-11-2011-12.xlsx
+++ b/Team-Data/2011-12/2-11-2011-12.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,16 +806,16 @@
         <v>4.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AF2" t="n">
         <v>5</v>
       </c>
       <c r="AG2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AH2" t="n">
         <v>1</v>
@@ -763,7 +830,7 @@
         <v>12</v>
       </c>
       <c r="AL2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AM2" t="n">
         <v>18</v>
@@ -772,7 +839,7 @@
         <v>2</v>
       </c>
       <c r="AO2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP2" t="n">
         <v>15</v>
@@ -784,22 +851,22 @@
         <v>23</v>
       </c>
       <c r="AS2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY2" t="n">
         <v>10</v>
@@ -808,13 +875,13 @@
         <v>3</v>
       </c>
       <c r="BA2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BC2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>3.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
         <v>15</v>
@@ -930,19 +997,19 @@
         <v>12</v>
       </c>
       <c r="AG3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL3" t="n">
         <v>16</v>
@@ -954,7 +1021,7 @@
         <v>1</v>
       </c>
       <c r="AO3" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AP3" t="n">
         <v>27</v>
@@ -966,7 +1033,7 @@
         <v>30</v>
       </c>
       <c r="AS3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT3" t="n">
         <v>30</v>
@@ -990,7 +1057,7 @@
         <v>16</v>
       </c>
       <c r="BA3" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BB3" t="n">
         <v>26</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -1025,64 +1092,64 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E4" t="n">
         <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G4" t="n">
-        <v>0.111</v>
+        <v>0.115</v>
       </c>
       <c r="H4" t="n">
         <v>48.2</v>
       </c>
       <c r="I4" t="n">
-        <v>33.6</v>
+        <v>33.8</v>
       </c>
       <c r="J4" t="n">
-        <v>81</v>
+        <v>81.2</v>
       </c>
       <c r="K4" t="n">
-        <v>0.414</v>
+        <v>0.417</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="M4" t="n">
         <v>13.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0.292</v>
+        <v>0.301</v>
       </c>
       <c r="O4" t="n">
-        <v>15.2</v>
+        <v>14.5</v>
       </c>
       <c r="P4" t="n">
-        <v>20.6</v>
+        <v>19.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.736</v>
+        <v>0.733</v>
       </c>
       <c r="R4" t="n">
-        <v>10.4</v>
+        <v>10.5</v>
       </c>
       <c r="S4" t="n">
-        <v>29.7</v>
+        <v>30</v>
       </c>
       <c r="T4" t="n">
-        <v>40.1</v>
+        <v>40.5</v>
       </c>
       <c r="U4" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="V4" t="n">
-        <v>14.7</v>
+        <v>15.1</v>
       </c>
       <c r="W4" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="X4" t="n">
         <v>5.6</v>
@@ -1094,34 +1161,34 @@
         <v>19.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>19.1</v>
+        <v>18.8</v>
       </c>
       <c r="AB4" t="n">
         <v>86.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>-14.6</v>
+        <v>-14.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE4" t="n">
         <v>30</v>
       </c>
       <c r="AF4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG4" t="n">
         <v>30</v>
       </c>
       <c r="AH4" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI4" t="n">
         <v>26</v>
       </c>
       <c r="AJ4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AK4" t="n">
         <v>29</v>
@@ -1133,22 +1200,22 @@
         <v>26</v>
       </c>
       <c r="AN4" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AO4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AP4" t="n">
+        <v>26</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>22</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>21</v>
       </c>
       <c r="AR4" t="n">
         <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AT4" t="n">
         <v>26</v>
@@ -1157,22 +1224,22 @@
         <v>22</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AW4" t="n">
         <v>29</v>
       </c>
       <c r="AX4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AZ4" t="n">
         <v>10</v>
       </c>
       <c r="BA4" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="BB4" t="n">
         <v>30</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1367,7 @@
         <v>28</v>
       </c>
       <c r="AI5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ5" t="n">
         <v>10</v>
@@ -1330,7 +1397,7 @@
         <v>2</v>
       </c>
       <c r="AS5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT5" t="n">
         <v>2</v>
@@ -1348,7 +1415,7 @@
         <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ5" t="n">
         <v>2</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -1389,118 +1456,118 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E6" t="n">
         <v>10</v>
       </c>
       <c r="F6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G6" t="n">
-        <v>0.385</v>
+        <v>0.4</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
       </c>
       <c r="I6" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="J6" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.43</v>
+        <v>0.433</v>
       </c>
       <c r="L6" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M6" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="N6" t="n">
-        <v>0.36</v>
+        <v>0.364</v>
       </c>
       <c r="O6" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="P6" t="n">
         <v>24.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.696</v>
+        <v>0.694</v>
       </c>
       <c r="R6" t="n">
         <v>12.7</v>
       </c>
       <c r="S6" t="n">
-        <v>30.3</v>
+        <v>30</v>
       </c>
       <c r="T6" t="n">
-        <v>43.1</v>
+        <v>42.7</v>
       </c>
       <c r="U6" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V6" t="n">
-        <v>16.2</v>
+        <v>16.4</v>
       </c>
       <c r="W6" t="n">
-        <v>7.7</v>
+        <v>7.9</v>
       </c>
       <c r="X6" t="n">
         <v>4.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Z6" t="n">
         <v>21</v>
       </c>
       <c r="AA6" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>94</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC6" t="n">
-        <v>-3.7</v>
+        <v>-3.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
         <v>22</v>
       </c>
       <c r="AF6" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AG6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>13</v>
       </c>
-      <c r="AI6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>12</v>
-      </c>
       <c r="AK6" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AL6" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AM6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AN6" t="n">
         <v>10</v>
       </c>
       <c r="AO6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AP6" t="n">
         <v>11</v>
@@ -1512,19 +1579,19 @@
         <v>3</v>
       </c>
       <c r="AS6" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV6" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AW6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX6" t="n">
         <v>23</v>
@@ -1533,16 +1600,16 @@
         <v>28</v>
       </c>
       <c r="AZ6" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>17</v>
+      </c>
+      <c r="BC6" t="n">
         <v>22</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>10</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>23</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -1571,64 +1638,64 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E7" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F7" t="n">
         <v>11</v>
       </c>
       <c r="G7" t="n">
-        <v>0.607</v>
+        <v>0.593</v>
       </c>
       <c r="H7" t="n">
-        <v>48.5</v>
+        <v>48.2</v>
       </c>
       <c r="I7" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J7" t="n">
-        <v>81.3</v>
+        <v>81.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.442</v>
+        <v>0.441</v>
       </c>
       <c r="L7" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="N7" t="n">
         <v>0.326</v>
       </c>
       <c r="O7" t="n">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="P7" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.738</v>
+        <v>0.74</v>
       </c>
       <c r="R7" t="n">
         <v>10.2</v>
       </c>
       <c r="S7" t="n">
-        <v>33.1</v>
+        <v>32.6</v>
       </c>
       <c r="T7" t="n">
-        <v>43.3</v>
+        <v>42.8</v>
       </c>
       <c r="U7" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V7" t="n">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
       <c r="W7" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X7" t="n">
         <v>5.6</v>
@@ -1637,22 +1704,22 @@
         <v>4.4</v>
       </c>
       <c r="Z7" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>94.7</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AC7" t="n">
         <v>3.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF7" t="n">
         <v>9</v>
@@ -1661,13 +1728,13 @@
         <v>9</v>
       </c>
       <c r="AH7" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
         <v>16</v>
       </c>
       <c r="AJ7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AK7" t="n">
         <v>16</v>
@@ -1682,7 +1749,7 @@
         <v>21</v>
       </c>
       <c r="AO7" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AP7" t="n">
         <v>18</v>
@@ -1691,25 +1758,25 @@
         <v>19</v>
       </c>
       <c r="AR7" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW7" t="n">
         <v>3</v>
       </c>
-      <c r="AT7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4</v>
-      </c>
       <c r="AX7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY7" t="n">
         <v>6</v>
@@ -1718,7 +1785,7 @@
         <v>15</v>
       </c>
       <c r="BA7" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BB7" t="n">
         <v>16</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -1753,25 +1820,25 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E8" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F8" t="n">
         <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>0.571</v>
+        <v>0.556</v>
       </c>
       <c r="H8" t="n">
         <v>48.7</v>
       </c>
       <c r="I8" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="J8" t="n">
-        <v>79.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K8" t="n">
         <v>0.476</v>
@@ -1780,37 +1847,37 @@
         <v>6.9</v>
       </c>
       <c r="M8" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0.33</v>
+        <v>0.332</v>
       </c>
       <c r="O8" t="n">
         <v>21</v>
       </c>
       <c r="P8" t="n">
-        <v>28.3</v>
+        <v>28.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.741</v>
+        <v>0.745</v>
       </c>
       <c r="R8" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S8" t="n">
-        <v>32.6</v>
+        <v>32.9</v>
       </c>
       <c r="T8" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U8" t="n">
-        <v>23.3</v>
+        <v>23.6</v>
       </c>
       <c r="V8" t="n">
-        <v>16.1</v>
+        <v>16.3</v>
       </c>
       <c r="W8" t="n">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="X8" t="n">
         <v>4.9</v>
@@ -1819,22 +1886,22 @@
         <v>6.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.9</v>
+        <v>103.6</v>
       </c>
       <c r="AC8" t="n">
         <v>3.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF8" t="n">
         <v>12</v>
@@ -1846,7 +1913,7 @@
         <v>3</v>
       </c>
       <c r="AI8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AJ8" t="n">
         <v>21</v>
@@ -1855,13 +1922,13 @@
         <v>2</v>
       </c>
       <c r="AL8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AM8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO8" t="n">
         <v>2</v>
@@ -1870,34 +1937,34 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR8" t="n">
         <v>29</v>
       </c>
       <c r="AS8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AT8" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AW8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX8" t="n">
         <v>18</v>
       </c>
       <c r="AY8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-8.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
         <v>26</v>
@@ -2034,7 +2101,7 @@
         <v>27</v>
       </c>
       <c r="AK9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL9" t="n">
         <v>25</v>
@@ -2049,7 +2116,7 @@
         <v>19</v>
       </c>
       <c r="AP9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ9" t="n">
         <v>6</v>
@@ -2061,13 +2128,13 @@
         <v>29</v>
       </c>
       <c r="AT9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AU9" t="n">
         <v>23</v>
       </c>
       <c r="AV9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW9" t="n">
         <v>22</v>
@@ -2076,7 +2143,7 @@
         <v>30</v>
       </c>
       <c r="AY9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ9" t="n">
         <v>9</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -2204,13 +2271,13 @@
         <v>18</v>
       </c>
       <c r="AG10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH10" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ10" t="n">
         <v>9</v>
@@ -2222,25 +2289,25 @@
         <v>3</v>
       </c>
       <c r="AM10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AQ10" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AR10" t="n">
         <v>24</v>
       </c>
       <c r="AS10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT10" t="n">
         <v>27</v>
@@ -2249,10 +2316,10 @@
         <v>2</v>
       </c>
       <c r="AV10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
         <v>5</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -2377,19 +2444,19 @@
         <v>2.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AF11" t="n">
         <v>9</v>
       </c>
       <c r="AG11" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI11" t="n">
         <v>1</v>
@@ -2401,10 +2468,10 @@
         <v>10</v>
       </c>
       <c r="AL11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM11" t="n">
         <v>11</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>12</v>
       </c>
       <c r="AN11" t="n">
         <v>15</v>
@@ -2419,31 +2486,31 @@
         <v>2</v>
       </c>
       <c r="AR11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS11" t="n">
         <v>12</v>
       </c>
       <c r="AT11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU11" t="n">
         <v>13</v>
       </c>
       <c r="AV11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AW11" t="n">
         <v>18</v>
       </c>
       <c r="AX11" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY11" t="n">
         <v>14</v>
       </c>
-      <c r="AY11" t="n">
-        <v>15</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA11" t="n">
         <v>29</v>
@@ -2452,7 +2519,7 @@
         <v>6</v>
       </c>
       <c r="BC11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -2481,100 +2548,100 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E12" t="n">
         <v>17</v>
       </c>
       <c r="F12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G12" t="n">
-        <v>0.63</v>
+        <v>0.654</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
       </c>
       <c r="I12" t="n">
-        <v>34.6</v>
+        <v>34.3</v>
       </c>
       <c r="J12" t="n">
         <v>80.8</v>
       </c>
       <c r="K12" t="n">
-        <v>0.429</v>
+        <v>0.425</v>
       </c>
       <c r="L12" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M12" t="n">
-        <v>15.3</v>
+        <v>15</v>
       </c>
       <c r="N12" t="n">
-        <v>0.37</v>
+        <v>0.371</v>
       </c>
       <c r="O12" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="P12" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.789</v>
+        <v>0.79</v>
       </c>
       <c r="R12" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="S12" t="n">
-        <v>31.8</v>
+        <v>32</v>
       </c>
       <c r="T12" t="n">
-        <v>43.8</v>
+        <v>44.3</v>
       </c>
       <c r="U12" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="V12" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="W12" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X12" t="n">
         <v>5.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z12" t="n">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="AA12" t="n">
         <v>21</v>
       </c>
       <c r="AB12" t="n">
-        <v>94.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE12" t="n">
         <v>7</v>
       </c>
       <c r="AF12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AG12" t="n">
         <v>8</v>
       </c>
       <c r="AH12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AJ12" t="n">
         <v>16</v>
@@ -2595,25 +2662,25 @@
         <v>5</v>
       </c>
       <c r="AP12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ12" t="n">
         <v>3</v>
       </c>
       <c r="AR12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="AS12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AT12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AW12" t="n">
         <v>8</v>
@@ -2631,10 +2698,10 @@
         <v>11</v>
       </c>
       <c r="BB12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -2663,88 +2730,88 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F13" t="n">
         <v>8</v>
       </c>
       <c r="G13" t="n">
-        <v>0.68</v>
+        <v>0.667</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J13" t="n">
-        <v>80.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.46</v>
+        <v>0.457</v>
       </c>
       <c r="L13" t="n">
         <v>7.7</v>
       </c>
       <c r="M13" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.356</v>
+        <v>0.354</v>
       </c>
       <c r="O13" t="n">
-        <v>16.9</v>
+        <v>16.8</v>
       </c>
       <c r="P13" t="n">
         <v>25</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.678</v>
+        <v>0.67</v>
       </c>
       <c r="R13" t="n">
         <v>11.4</v>
       </c>
       <c r="S13" t="n">
-        <v>30</v>
+        <v>29.8</v>
       </c>
       <c r="T13" t="n">
-        <v>41.4</v>
+        <v>41.1</v>
       </c>
       <c r="U13" t="n">
-        <v>22</v>
+        <v>21.7</v>
       </c>
       <c r="V13" t="n">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="W13" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="X13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>22.4</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>98.2</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE13" t="n">
         <v>8</v>
-      </c>
-      <c r="X13" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>21.7</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>22.3</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>98.7</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>28</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>7</v>
       </c>
       <c r="AF13" t="n">
         <v>4</v>
@@ -2753,7 +2820,7 @@
         <v>4</v>
       </c>
       <c r="AH13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AI13" t="n">
         <v>9</v>
@@ -2762,7 +2829,7 @@
         <v>18</v>
       </c>
       <c r="AK13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AL13" t="n">
         <v>4</v>
@@ -2771,13 +2838,13 @@
         <v>4</v>
       </c>
       <c r="AN13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP13" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ13" t="n">
         <v>29</v>
@@ -2786,16 +2853,16 @@
         <v>15</v>
       </c>
       <c r="AS13" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AT13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AU13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW13" t="n">
         <v>12</v>
@@ -2804,7 +2871,7 @@
         <v>10</v>
       </c>
       <c r="AY13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ13" t="n">
         <v>25</v>
@@ -2813,10 +2880,10 @@
         <v>4</v>
       </c>
       <c r="BB13" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BC13" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BD13" t="n">
         <v>10</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -2923,25 +2990,25 @@
         <v>1.8</v>
       </c>
       <c r="AD14" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF14" t="n">
         <v>12</v>
       </c>
       <c r="AG14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AI14" t="n">
         <v>17</v>
       </c>
       <c r="AJ14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK14" t="n">
         <v>13</v>
@@ -2956,7 +3023,7 @@
         <v>30</v>
       </c>
       <c r="AO14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AP14" t="n">
         <v>12</v>
@@ -2977,7 +3044,7 @@
         <v>16</v>
       </c>
       <c r="AV14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
         <v>30</v>
@@ -2998,7 +3065,7 @@
         <v>21</v>
       </c>
       <c r="BC14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -3105,22 +3172,22 @@
         <v>1</v>
       </c>
       <c r="AD15" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE15" t="n">
         <v>15</v>
       </c>
       <c r="AF15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG15" t="n">
         <v>17</v>
       </c>
       <c r="AH15" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ15" t="n">
         <v>7</v>
@@ -3138,7 +3205,7 @@
         <v>23</v>
       </c>
       <c r="AO15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP15" t="n">
         <v>14</v>
@@ -3147,19 +3214,19 @@
         <v>14</v>
       </c>
       <c r="AR15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AS15" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU15" t="n">
         <v>25</v>
       </c>
       <c r="AV15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW15" t="n">
         <v>1</v>
@@ -3168,7 +3235,7 @@
         <v>17</v>
       </c>
       <c r="AY15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ15" t="n">
         <v>13</v>
@@ -3180,7 +3247,7 @@
         <v>21</v>
       </c>
       <c r="BC15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>7.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
         <v>3</v>
@@ -3305,7 +3372,7 @@
         <v>2</v>
       </c>
       <c r="AJ16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK16" t="n">
         <v>1</v>
@@ -3335,7 +3402,7 @@
         <v>5</v>
       </c>
       <c r="AT16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU16" t="n">
         <v>14</v>
@@ -3350,10 +3417,10 @@
         <v>20</v>
       </c>
       <c r="AY16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA16" t="n">
         <v>5</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -3391,64 +3458,64 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E17" t="n">
         <v>12</v>
       </c>
       <c r="F17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.444</v>
+        <v>0.462</v>
       </c>
       <c r="H17" t="n">
         <v>48.2</v>
       </c>
       <c r="I17" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J17" t="n">
-        <v>84</v>
+        <v>83.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.431</v>
+        <v>0.432</v>
       </c>
       <c r="L17" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M17" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0.334</v>
+        <v>0.331</v>
       </c>
       <c r="O17" t="n">
-        <v>16.2</v>
+        <v>16.5</v>
       </c>
       <c r="P17" t="n">
-        <v>20.6</v>
+        <v>21.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.786</v>
+        <v>0.783</v>
       </c>
       <c r="R17" t="n">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="S17" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="T17" t="n">
-        <v>41.6</v>
+        <v>41.3</v>
       </c>
       <c r="U17" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="V17" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W17" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X17" t="n">
         <v>5.1</v>
@@ -3457,91 +3524,91 @@
         <v>5.1</v>
       </c>
       <c r="Z17" t="n">
+        <v>19.8</v>
+      </c>
+      <c r="AA17" t="n">
         <v>19.6</v>
       </c>
-      <c r="AA17" t="n">
-        <v>19.4</v>
-      </c>
       <c r="AB17" t="n">
-        <v>95.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>-1.1</v>
+        <v>-0.9</v>
       </c>
       <c r="AD17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>19</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>14</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL17" t="n">
         <v>13</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>13</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>12</v>
       </c>
       <c r="AM17" t="n">
         <v>8</v>
       </c>
       <c r="AN17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO17" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AP17" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AQ17" t="n">
         <v>4</v>
       </c>
       <c r="AR17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="AS17" t="n">
         <v>27</v>
       </c>
       <c r="AT17" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AU17" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV17" t="n">
         <v>10</v>
       </c>
-      <c r="AV17" t="n">
-        <v>8</v>
-      </c>
       <c r="AW17" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AX17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ17" t="n">
         <v>14</v>
       </c>
       <c r="BA17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC17" t="n">
         <v>20</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E18" t="n">
         <v>13</v>
       </c>
       <c r="F18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G18" t="n">
-        <v>0.464</v>
+        <v>0.481</v>
       </c>
       <c r="H18" t="n">
         <v>48</v>
@@ -3591,13 +3658,13 @@
         <v>34.6</v>
       </c>
       <c r="J18" t="n">
-        <v>80.8</v>
+        <v>80.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0.429</v>
+        <v>0.428</v>
       </c>
       <c r="L18" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="M18" t="n">
         <v>20</v>
@@ -3606,19 +3673,19 @@
         <v>0.327</v>
       </c>
       <c r="O18" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="P18" t="n">
-        <v>26.5</v>
+        <v>26.8</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.771</v>
+        <v>0.767</v>
       </c>
       <c r="R18" t="n">
         <v>12.1</v>
       </c>
       <c r="S18" t="n">
-        <v>32.5</v>
+        <v>32.3</v>
       </c>
       <c r="T18" t="n">
         <v>44.5</v>
@@ -3627,37 +3694,37 @@
         <v>18.4</v>
       </c>
       <c r="V18" t="n">
-        <v>16.4</v>
+        <v>16.1</v>
       </c>
       <c r="W18" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X18" t="n">
         <v>4</v>
       </c>
       <c r="Y18" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="Z18" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AA18" t="n">
         <v>22.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>96.3</v>
+        <v>96.2</v>
       </c>
       <c r="AC18" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
         <v>17</v>
       </c>
       <c r="AF18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG18" t="n">
         <v>18</v>
@@ -3669,13 +3736,13 @@
         <v>20</v>
       </c>
       <c r="AJ18" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AK18" t="n">
         <v>24</v>
       </c>
       <c r="AL18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM18" t="n">
         <v>10</v>
@@ -3690,10 +3757,10 @@
         <v>4</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AR18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS18" t="n">
         <v>7</v>
@@ -3705,19 +3772,19 @@
         <v>26</v>
       </c>
       <c r="AV18" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AW18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX18" t="n">
         <v>29</v>
       </c>
       <c r="AY18" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AZ18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA18" t="n">
         <v>3</v>
@@ -3726,7 +3793,7 @@
         <v>11</v>
       </c>
       <c r="BC18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -3755,16 +3822,16 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E19" t="n">
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G19" t="n">
-        <v>0.276</v>
+        <v>0.286</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
@@ -3773,46 +3840,46 @@
         <v>33.3</v>
       </c>
       <c r="J19" t="n">
-        <v>79.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="K19" t="n">
         <v>0.422</v>
       </c>
       <c r="L19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="M19" t="n">
         <v>24.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.353</v>
+        <v>0.355</v>
       </c>
       <c r="O19" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="P19" t="n">
-        <v>21.8</v>
+        <v>22</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.772</v>
+        <v>0.771</v>
       </c>
       <c r="R19" t="n">
         <v>12.2</v>
       </c>
       <c r="S19" t="n">
-        <v>26.7</v>
+        <v>26.8</v>
       </c>
       <c r="T19" t="n">
         <v>39</v>
       </c>
       <c r="U19" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V19" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W19" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X19" t="n">
         <v>4.1</v>
@@ -3821,37 +3888,37 @@
         <v>5.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>20.1</v>
+        <v>20.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>92.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-7.7</v>
+        <v>-7.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE19" t="n">
         <v>26</v>
       </c>
       <c r="AF19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AH19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI19" t="n">
         <v>28</v>
       </c>
       <c r="AJ19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AK19" t="n">
         <v>26</v>
@@ -3863,19 +3930,19 @@
         <v>2</v>
       </c>
       <c r="AN19" t="n">
+        <v>11</v>
+      </c>
+      <c r="AO19" t="n">
         <v>12</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>14</v>
       </c>
       <c r="AP19" t="n">
         <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AR19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AS19" t="n">
         <v>30</v>
@@ -3887,22 +3954,22 @@
         <v>19</v>
       </c>
       <c r="AV19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AY19" t="n">
         <v>19</v>
       </c>
       <c r="AZ19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB19" t="n">
         <v>23</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
         <v>29</v>
@@ -4027,7 +4094,7 @@
         <v>29</v>
       </c>
       <c r="AH20" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI20" t="n">
         <v>24</v>
@@ -4045,13 +4112,13 @@
         <v>29</v>
       </c>
       <c r="AN20" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AP20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ20" t="n">
         <v>18</v>
@@ -4060,16 +4127,16 @@
         <v>14</v>
       </c>
       <c r="AS20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AT20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU20" t="n">
         <v>21</v>
       </c>
       <c r="AV20" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW20" t="n">
         <v>21</v>
@@ -4081,7 +4148,7 @@
         <v>22</v>
       </c>
       <c r="AZ20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA20" t="n">
         <v>26</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -4119,97 +4186,97 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F21" t="n">
         <v>15</v>
       </c>
       <c r="G21" t="n">
-        <v>0.464</v>
+        <v>0.444</v>
       </c>
       <c r="H21" t="n">
         <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>34.6</v>
+        <v>34.4</v>
       </c>
       <c r="J21" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="K21" t="n">
-        <v>0.43</v>
+        <v>0.429</v>
       </c>
       <c r="L21" t="n">
         <v>6.9</v>
       </c>
       <c r="M21" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0.302</v>
+        <v>0.3</v>
       </c>
       <c r="O21" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="P21" t="n">
-        <v>25.4</v>
+        <v>25.5</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.767</v>
+        <v>0.772</v>
       </c>
       <c r="R21" t="n">
-        <v>10.7</v>
+        <v>10.9</v>
       </c>
       <c r="S21" t="n">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="T21" t="n">
-        <v>41.5</v>
+        <v>41.6</v>
       </c>
       <c r="U21" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="V21" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="W21" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="X21" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="Y21" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z21" t="n">
         <v>22.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AB21" t="n">
-        <v>95.5</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC21" t="n">
         <v>0.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AF21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH21" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AI21" t="n">
         <v>22</v>
@@ -4218,10 +4285,10 @@
         <v>20</v>
       </c>
       <c r="AK21" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AM21" t="n">
         <v>3</v>
@@ -4230,28 +4297,28 @@
         <v>25</v>
       </c>
       <c r="AO21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AP21" t="n">
         <v>6</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AR21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS21" t="n">
         <v>18</v>
       </c>
       <c r="AT21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW21" t="n">
         <v>2</v>
@@ -4260,7 +4327,7 @@
         <v>25</v>
       </c>
       <c r="AY21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ21" t="n">
         <v>27</v>
@@ -4269,7 +4336,7 @@
         <v>2</v>
       </c>
       <c r="BB21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC21" t="n">
         <v>18</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>4.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,7 +4458,7 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
         <v>11</v>
@@ -4406,7 +4473,7 @@
         <v>14</v>
       </c>
       <c r="AM22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN22" t="n">
         <v>14</v>
@@ -4424,13 +4491,13 @@
         <v>21</v>
       </c>
       <c r="AS22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AU22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
@@ -4445,16 +4512,16 @@
         <v>11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB22" t="n">
         <v>3</v>
       </c>
       <c r="BC22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -4483,64 +4550,64 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F23" t="n">
         <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>0.607</v>
+        <v>0.593</v>
       </c>
       <c r="H23" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I23" t="n">
         <v>33.3</v>
       </c>
       <c r="J23" t="n">
-        <v>76.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="K23" t="n">
         <v>0.433</v>
       </c>
       <c r="L23" t="n">
-        <v>9.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>25.7</v>
+        <v>25.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0.387</v>
+        <v>0.386</v>
       </c>
       <c r="O23" t="n">
         <v>16.4</v>
       </c>
       <c r="P23" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.651</v>
+        <v>0.65</v>
       </c>
       <c r="R23" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S23" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="T23" t="n">
         <v>43.1</v>
       </c>
       <c r="U23" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V23" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W23" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X23" t="n">
         <v>4.1</v>
@@ -4549,22 +4616,22 @@
         <v>4.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>18.4</v>
+        <v>18.6</v>
       </c>
       <c r="AA23" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="AB23" t="n">
-        <v>92.90000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF23" t="n">
         <v>9</v>
@@ -4573,7 +4640,7 @@
         <v>9</v>
       </c>
       <c r="AH23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AI23" t="n">
         <v>29</v>
@@ -4594,7 +4661,7 @@
         <v>6</v>
       </c>
       <c r="AO23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP23" t="n">
         <v>7</v>
@@ -4606,31 +4673,31 @@
         <v>17</v>
       </c>
       <c r="AS23" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT23" t="n">
         <v>8</v>
-      </c>
-      <c r="AT23" t="n">
-        <v>9</v>
       </c>
       <c r="AU23" t="n">
         <v>20</v>
       </c>
       <c r="AV23" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AW23" t="n">
         <v>27</v>
       </c>
       <c r="AX23" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AY23" t="n">
         <v>7</v>
       </c>
       <c r="AZ23" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BA23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BB23" t="n">
         <v>20</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -4665,28 +4732,28 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F24" t="n">
         <v>9</v>
       </c>
       <c r="G24" t="n">
-        <v>0.679</v>
+        <v>0.667</v>
       </c>
       <c r="H24" t="n">
         <v>48.4</v>
       </c>
       <c r="I24" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J24" t="n">
-        <v>82.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="K24" t="n">
-        <v>0.459</v>
+        <v>0.46</v>
       </c>
       <c r="L24" t="n">
         <v>6.1</v>
@@ -4695,34 +4762,34 @@
         <v>15.7</v>
       </c>
       <c r="N24" t="n">
-        <v>0.39</v>
+        <v>0.388</v>
       </c>
       <c r="O24" t="n">
-        <v>13.8</v>
+        <v>13.4</v>
       </c>
       <c r="P24" t="n">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.717</v>
+        <v>0.715</v>
       </c>
       <c r="R24" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S24" t="n">
         <v>33.4</v>
       </c>
       <c r="T24" t="n">
-        <v>42.9</v>
+        <v>43</v>
       </c>
       <c r="U24" t="n">
         <v>22.4</v>
       </c>
       <c r="V24" t="n">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
       <c r="W24" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="X24" t="n">
         <v>4.6</v>
@@ -4734,16 +4801,16 @@
         <v>17.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="AB24" t="n">
-        <v>95.8</v>
+        <v>95.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>9.1</v>
+        <v>8.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
         <v>4</v>
@@ -4752,28 +4819,28 @@
         <v>5</v>
       </c>
       <c r="AG24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH24" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AI24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ24" t="n">
         <v>6</v>
       </c>
       <c r="AK24" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AL24" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM24" t="n">
         <v>20</v>
       </c>
       <c r="AN24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4791,7 +4858,7 @@
         <v>2</v>
       </c>
       <c r="AT24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AU24" t="n">
         <v>5</v>
@@ -4800,13 +4867,13 @@
         <v>1</v>
       </c>
       <c r="AW24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX24" t="n">
         <v>22</v>
       </c>
       <c r="AY24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AZ24" t="n">
         <v>4</v>
@@ -4815,7 +4882,7 @@
         <v>30</v>
       </c>
       <c r="BB24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC24" t="n">
         <v>2</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -4847,109 +4914,109 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F25" t="n">
         <v>15</v>
       </c>
       <c r="G25" t="n">
-        <v>0.444</v>
+        <v>0.423</v>
       </c>
       <c r="H25" t="n">
         <v>48</v>
       </c>
       <c r="I25" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J25" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.448</v>
+        <v>0.446</v>
       </c>
       <c r="L25" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M25" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N25" t="n">
         <v>0.351</v>
       </c>
       <c r="O25" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="P25" t="n">
-        <v>18.4</v>
+        <v>18.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="R25" t="n">
-        <v>9.9</v>
+        <v>10</v>
       </c>
       <c r="S25" t="n">
         <v>31</v>
       </c>
       <c r="T25" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U25" t="n">
-        <v>21.6</v>
+        <v>21.4</v>
       </c>
       <c r="V25" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W25" t="n">
         <v>6.8</v>
       </c>
       <c r="X25" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="n">
         <v>4</v>
       </c>
       <c r="Z25" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>19.3</v>
+        <v>19.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>93.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="AC25" t="n">
-        <v>-2.7</v>
+        <v>-3.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AG25" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH25" t="n">
         <v>28</v>
       </c>
       <c r="AI25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK25" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL25" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="AM25" t="n">
         <v>13</v>
@@ -4967,7 +5034,7 @@
         <v>10</v>
       </c>
       <c r="AR25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AS25" t="n">
         <v>16</v>
@@ -4976,22 +5043,22 @@
         <v>25</v>
       </c>
       <c r="AU25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW25" t="n">
         <v>25</v>
       </c>
       <c r="AX25" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AY25" t="n">
         <v>2</v>
       </c>
       <c r="AZ25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA25" t="n">
         <v>18</v>
@@ -5000,7 +5067,7 @@
         <v>19</v>
       </c>
       <c r="BC25" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -5029,64 +5096,64 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E26" t="n">
         <v>15</v>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G26" t="n">
-        <v>0.536</v>
+        <v>0.556</v>
       </c>
       <c r="H26" t="n">
-        <v>48.7</v>
+        <v>48.4</v>
       </c>
       <c r="I26" t="n">
         <v>37.1</v>
       </c>
       <c r="J26" t="n">
-        <v>83.40000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.444</v>
+        <v>0.448</v>
       </c>
       <c r="L26" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M26" t="n">
         <v>19.3</v>
       </c>
       <c r="N26" t="n">
-        <v>0.311</v>
+        <v>0.317</v>
       </c>
       <c r="O26" t="n">
         <v>18</v>
       </c>
       <c r="P26" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.785</v>
+        <v>0.781</v>
       </c>
       <c r="R26" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S26" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="T26" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U26" t="n">
-        <v>21.8</v>
+        <v>22.1</v>
       </c>
       <c r="V26" t="n">
         <v>14.4</v>
       </c>
       <c r="W26" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="X26" t="n">
         <v>5.4</v>
@@ -5095,31 +5162,31 @@
         <v>5</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA26" t="n">
         <v>21.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.09999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AF26" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AG26" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AH26" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AI26" t="n">
         <v>8</v>
@@ -5128,10 +5195,10 @@
         <v>5</v>
       </c>
       <c r="AK26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL26" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AM26" t="n">
         <v>14</v>
@@ -5155,16 +5222,16 @@
         <v>14</v>
       </c>
       <c r="AT26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV26" t="n">
         <v>7</v>
       </c>
       <c r="AW26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AX26" t="n">
         <v>9</v>
@@ -5173,13 +5240,13 @@
         <v>12</v>
       </c>
       <c r="AZ26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BA26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BC26" t="n">
         <v>4</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -5211,28 +5278,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E27" t="n">
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G27" t="n">
-        <v>0.37</v>
+        <v>0.385</v>
       </c>
       <c r="H27" t="n">
         <v>48.2</v>
       </c>
       <c r="I27" t="n">
-        <v>33.7</v>
+        <v>34</v>
       </c>
       <c r="J27" t="n">
-        <v>83.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="K27" t="n">
-        <v>0.404</v>
+        <v>0.406</v>
       </c>
       <c r="L27" t="n">
         <v>6.1</v>
@@ -5241,25 +5308,25 @@
         <v>20.3</v>
       </c>
       <c r="N27" t="n">
-        <v>0.303</v>
+        <v>0.3</v>
       </c>
       <c r="O27" t="n">
-        <v>18.4</v>
+        <v>18.3</v>
       </c>
       <c r="P27" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.736</v>
+        <v>0.734</v>
       </c>
       <c r="R27" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="S27" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T27" t="n">
-        <v>43.7</v>
+        <v>43.8</v>
       </c>
       <c r="U27" t="n">
         <v>16.5</v>
@@ -5268,28 +5335,28 @@
         <v>15.8</v>
       </c>
       <c r="W27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X27" t="n">
         <v>4.1</v>
       </c>
       <c r="Y27" t="n">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>19.5</v>
+        <v>19.3</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AB27" t="n">
-        <v>92</v>
+        <v>92.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>-8.5</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="AE27" t="n">
         <v>22</v>
@@ -5301,40 +5368,40 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI27" t="n">
         <v>25</v>
       </c>
       <c r="AJ27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AK27" t="n">
         <v>30</v>
       </c>
       <c r="AL27" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AM27" t="n">
         <v>9</v>
       </c>
       <c r="AN27" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO27" t="n">
         <v>8</v>
       </c>
       <c r="AP27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR27" t="n">
         <v>1</v>
       </c>
       <c r="AS27" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AT27" t="n">
         <v>6</v>
@@ -5349,16 +5416,16 @@
         <v>11</v>
       </c>
       <c r="AX27" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AY27" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ27" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB27" t="n">
         <v>24</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -5393,46 +5460,46 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F28" t="n">
         <v>9</v>
       </c>
       <c r="G28" t="n">
-        <v>0.679</v>
+        <v>0.667</v>
       </c>
       <c r="H28" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I28" t="n">
-        <v>37.8</v>
+        <v>37.6</v>
       </c>
       <c r="J28" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>0.461</v>
+        <v>0.458</v>
       </c>
       <c r="L28" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="M28" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.383</v>
+        <v>0.385</v>
       </c>
       <c r="O28" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="P28" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.725</v>
+        <v>0.726</v>
       </c>
       <c r="R28" t="n">
         <v>10</v>
@@ -5441,10 +5508,10 @@
         <v>31.8</v>
       </c>
       <c r="T28" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U28" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="V28" t="n">
         <v>13.6</v>
@@ -5462,16 +5529,16 @@
         <v>17</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="AB28" t="n">
-        <v>98</v>
+        <v>97.8</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="AD28" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
         <v>4</v>
@@ -5480,10 +5547,10 @@
         <v>5</v>
       </c>
       <c r="AG28" t="n">
+        <v>4</v>
+      </c>
+      <c r="AH28" t="n">
         <v>5</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>7</v>
       </c>
       <c r="AI28" t="n">
         <v>7</v>
@@ -5492,43 +5559,43 @@
         <v>8</v>
       </c>
       <c r="AK28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN28" t="n">
         <v>7</v>
       </c>
       <c r="AO28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AQ28" t="n">
         <v>25</v>
       </c>
       <c r="AR28" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AS28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT28" t="n">
         <v>19</v>
       </c>
       <c r="AU28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV28" t="n">
         <v>2</v>
       </c>
       <c r="AW28" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX28" t="n">
         <v>24</v>
@@ -5540,13 +5607,13 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BB28" t="n">
         <v>8</v>
       </c>
       <c r="BC28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-5.6</v>
       </c>
       <c r="AD29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
         <v>24</v>
@@ -5665,7 +5732,7 @@
         <v>25</v>
       </c>
       <c r="AH29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI29" t="n">
         <v>30</v>
@@ -5686,7 +5753,7 @@
         <v>19</v>
       </c>
       <c r="AO29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP29" t="n">
         <v>20</v>
@@ -5695,7 +5762,7 @@
         <v>13</v>
       </c>
       <c r="AR29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS29" t="n">
         <v>15</v>
@@ -5704,7 +5771,7 @@
         <v>18</v>
       </c>
       <c r="AU29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV29" t="n">
         <v>19</v>
@@ -5713,7 +5780,7 @@
         <v>26</v>
       </c>
       <c r="AX29" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY29" t="n">
         <v>18</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-0.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE30" t="n">
         <v>17</v>
@@ -5847,13 +5914,13 @@
         <v>16</v>
       </c>
       <c r="AH30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI30" t="n">
         <v>10</v>
       </c>
       <c r="AJ30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK30" t="n">
         <v>11</v>
@@ -5865,16 +5932,16 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO30" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP30" t="n">
         <v>5</v>
       </c>
       <c r="AQ30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR30" t="n">
         <v>13</v>
@@ -5883,7 +5950,7 @@
         <v>17</v>
       </c>
       <c r="AT30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU30" t="n">
         <v>15</v>
@@ -5892,7 +5959,7 @@
         <v>6</v>
       </c>
       <c r="AW30" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AX30" t="n">
         <v>3</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-10.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
@@ -6029,13 +6096,13 @@
         <v>28</v>
       </c>
       <c r="AH31" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AK31" t="n">
         <v>27</v>
@@ -6047,7 +6114,7 @@
         <v>25</v>
       </c>
       <c r="AN31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO31" t="n">
         <v>21</v>
@@ -6059,22 +6126,22 @@
         <v>26</v>
       </c>
       <c r="AR31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS31" t="n">
         <v>28</v>
       </c>
       <c r="AT31" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AU31" t="n">
         <v>29</v>
       </c>
       <c r="AV31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX31" t="n">
         <v>2</v>
@@ -6086,7 +6153,7 @@
         <v>26</v>
       </c>
       <c r="BA31" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BB31" t="n">
         <v>25</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-11-2011-12</t>
+          <t>2012-02-11</t>
         </is>
       </c>
     </row>
